--- a/Test upload format/Mudra/IA/2026 - 2027/CP1 26-27.xlsx
+++ b/Test upload format/Mudra/IA/2026 - 2027/CP1 26-27.xlsx
@@ -1,14 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180"/>
+    <workbookView windowWidth="24000" windowHeight="9600"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$T$22</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -27,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="54">
   <si>
     <t>custid</t>
   </si>
@@ -89,37 +92,106 @@
     <t>HomeStay</t>
   </si>
   <si>
-    <t>part1</t>
+    <t>2627CR720</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>01-07-2027</t>
+  </si>
+  <si>
+    <t>40000</t>
+  </si>
+  <si>
+    <t>01-04-2026</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>01-04-2026</t>
-  </si>
-  <si>
-    <t>J</t>
-  </si>
-  <si>
-    <t>part2</t>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>2627CR721</t>
+  </si>
+  <si>
+    <t>10000</t>
   </si>
   <si>
     <t>IA</t>
   </si>
   <si>
-    <t>01-07-2027</t>
-  </si>
-  <si>
-    <t>Y</t>
+    <t>T</t>
+  </si>
+  <si>
+    <t>2627CR722</t>
   </si>
   <si>
     <t>S</t>
   </si>
   <si>
-    <t>part3</t>
-  </si>
-  <si>
-    <t>K</t>
+    <t>2627CR701</t>
+  </si>
+  <si>
+    <t>2627CR703</t>
+  </si>
+  <si>
+    <t>2627CR704</t>
+  </si>
+  <si>
+    <t>2627CR705</t>
+  </si>
+  <si>
+    <t>2627CR706</t>
+  </si>
+  <si>
+    <t>2627CR707</t>
+  </si>
+  <si>
+    <t>2627CR708</t>
+  </si>
+  <si>
+    <t>2627CR709</t>
+  </si>
+  <si>
+    <t>2627CR710</t>
+  </si>
+  <si>
+    <t>2627CR711</t>
+  </si>
+  <si>
+    <t>2627CR712</t>
+  </si>
+  <si>
+    <t>2627CR713</t>
+  </si>
+  <si>
+    <t>2627CR714</t>
+  </si>
+  <si>
+    <t>2627CR715</t>
+  </si>
+  <si>
+    <t>2627CR716</t>
+  </si>
+  <si>
+    <t>2627CR717</t>
+  </si>
+  <si>
+    <t>2627CR718</t>
+  </si>
+  <si>
+    <t>2627CR719</t>
+  </si>
+  <si>
+    <t>2627CR724</t>
   </si>
 </sst>
 </file>
@@ -132,7 +204,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -147,12 +219,6 @@
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -299,7 +365,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -308,7 +374,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.8"/>
+        <fgColor theme="5" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -499,7 +595,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -519,21 +615,6 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -653,137 +734,138 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -794,16 +876,28 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1123,13 +1217,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="3"/>
+  <dimension ref="A1:T22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.8571428571429" customWidth="1"/>
     <col min="2" max="2" width="24.5714285714286" customWidth="1"/>
     <col min="3" max="3" width="15.2857142857143" customWidth="1"/>
-    <col min="4" max="4" width="11.5714285714286" customWidth="1"/>
+    <col min="4" max="4" width="13.8571428571429" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
     <col min="6" max="6" width="20.5714285714286" customWidth="1"/>
     <col min="7" max="7" width="19" customWidth="1"/>
@@ -1147,58 +1241,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="P1" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="Q1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="R1" s="6" t="s">
         <v>17</v>
       </c>
       <c r="S1" t="s">
@@ -1208,81 +1302,79 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" customFormat="1" spans="1:20">
-      <c r="A2" s="6" t="s">
+    <row r="2" s="1" customFormat="1" spans="1:20">
+      <c r="A2" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="6">
-        <v>1000</v>
-      </c>
-      <c r="D2" s="7" t="s">
+      <c r="C2" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="8"/>
-      <c r="F2" s="6">
-        <v>9000</v>
-      </c>
-      <c r="G2" s="8" t="s">
+      <c r="D2" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="H2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" s="8"/>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2" s="8">
+      <c r="E2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="9"/>
+      <c r="J2" s="1">
+        <v>1</v>
+      </c>
+      <c r="K2" s="9">
         <v>0</v>
       </c>
-      <c r="L2" s="8">
-        <v>1</v>
-      </c>
-      <c r="M2" s="6">
-        <v>9999.9</v>
-      </c>
-      <c r="N2" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="S2" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="T2" t="s">
-        <v>21</v>
+      <c r="L2" s="9">
+        <v>1</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="S2" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:20">
-      <c r="A3" s="9" t="s">
+    <row r="3" s="2" customFormat="1" spans="1:20">
+      <c r="A3" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="9">
-        <v>10000</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="F3" s="9">
-        <v>400000</v>
-      </c>
       <c r="G3" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="J3" s="1">
+        <v>25</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="11"/>
+      <c r="J3" s="2">
         <v>1</v>
       </c>
       <c r="K3" s="11">
@@ -1291,46 +1383,44 @@
       <c r="L3" s="11">
         <v>1</v>
       </c>
-      <c r="M3" s="9">
-        <v>605501.57</v>
+      <c r="M3" s="14" t="s">
+        <v>27</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="S3" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>21</v>
+        <v>32</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:20">
-      <c r="A4" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="9">
-        <v>1000</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" s="9">
-        <v>100000</v>
+    <row r="4" s="2" customFormat="1" spans="1:20">
+      <c r="A4" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11" t="s">
+        <v>24</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="I4" s="11"/>
-      <c r="J4" s="1">
+      <c r="J4" s="2">
         <v>1</v>
       </c>
       <c r="K4" s="11">
@@ -1339,20 +1429,870 @@
       <c r="L4" s="11">
         <v>1</v>
       </c>
-      <c r="M4" s="9">
-        <v>200000.56</v>
+      <c r="M4" s="14" t="s">
+        <v>27</v>
       </c>
       <c r="N4" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="S4" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20">
+      <c r="A5" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" t="s">
         <v>22</v>
       </c>
-      <c r="S4" s="11" t="s">
+      <c r="I5" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5" s="16">
+        <v>0</v>
+      </c>
+      <c r="L5" s="16">
+        <v>1</v>
+      </c>
+      <c r="M5" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="N5" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="S5" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="T5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20">
+      <c r="A6" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="T4" s="1" t="s">
-        <v>21</v>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6" s="16">
+        <v>0</v>
+      </c>
+      <c r="L6" s="16">
+        <v>1</v>
+      </c>
+      <c r="M6" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="N6" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="S6" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="T6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20">
+      <c r="A7" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7" s="16">
+        <v>0</v>
+      </c>
+      <c r="L7" s="16">
+        <v>1</v>
+      </c>
+      <c r="M7" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="N7" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="S7" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="T7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20">
+      <c r="A8" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8" s="16">
+        <v>0</v>
+      </c>
+      <c r="L8" s="16">
+        <v>1</v>
+      </c>
+      <c r="M8" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="N8" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="S8" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="T8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20">
+      <c r="A9" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9" s="16">
+        <v>0</v>
+      </c>
+      <c r="L9" s="16">
+        <v>1</v>
+      </c>
+      <c r="M9" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="N9" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="S9" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="T9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20">
+      <c r="A10" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" t="s">
+        <v>22</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10" s="16">
+        <v>0</v>
+      </c>
+      <c r="L10" s="16">
+        <v>1</v>
+      </c>
+      <c r="M10" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="N10" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="S10" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="T10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20">
+      <c r="A11" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="H11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11" s="16">
+        <v>0</v>
+      </c>
+      <c r="L11" s="16">
+        <v>1</v>
+      </c>
+      <c r="M11" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="N11" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="S11" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="T11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20">
+      <c r="A12" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12" s="16">
+        <v>0</v>
+      </c>
+      <c r="L12" s="16">
+        <v>1</v>
+      </c>
+      <c r="M12" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="N12" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="S12" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="T12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20">
+      <c r="A13" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="G13" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="H13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13" s="16">
+        <v>0</v>
+      </c>
+      <c r="L13" s="16">
+        <v>1</v>
+      </c>
+      <c r="M13" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="N13" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="S13" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="T13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20">
+      <c r="A14" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="H14" t="s">
+        <v>22</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14" s="16">
+        <v>0</v>
+      </c>
+      <c r="L14" s="16">
+        <v>1</v>
+      </c>
+      <c r="M14" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="N14" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="S14" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="T14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20">
+      <c r="A15" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="G15" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="H15" t="s">
+        <v>22</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15" s="16">
+        <v>0</v>
+      </c>
+      <c r="L15" s="16">
+        <v>1</v>
+      </c>
+      <c r="M15" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="N15" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="S15" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="T15" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20">
+      <c r="A16" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="H16" t="s">
+        <v>22</v>
+      </c>
+      <c r="I16" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16" s="16">
+        <v>0</v>
+      </c>
+      <c r="L16" s="16">
+        <v>1</v>
+      </c>
+      <c r="M16" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="N16" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="S16" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="T16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20">
+      <c r="A17" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="G17" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="H17" t="s">
+        <v>22</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+      <c r="K17" s="16">
+        <v>0</v>
+      </c>
+      <c r="L17" s="16">
+        <v>1</v>
+      </c>
+      <c r="M17" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="N17" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="S17" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="T17" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20">
+      <c r="A18" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" t="s">
+        <v>26</v>
+      </c>
+      <c r="F18" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="G18" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="H18" t="s">
+        <v>22</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18" s="16">
+        <v>0</v>
+      </c>
+      <c r="L18" s="16">
+        <v>1</v>
+      </c>
+      <c r="M18" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="N18" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="S18" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="T18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20">
+      <c r="A19" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" t="s">
+        <v>26</v>
+      </c>
+      <c r="F19" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="G19" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="H19" t="s">
+        <v>22</v>
+      </c>
+      <c r="I19" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="K19" s="16">
+        <v>0</v>
+      </c>
+      <c r="L19" s="16">
+        <v>1</v>
+      </c>
+      <c r="M19" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="N19" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="S19" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="T19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20">
+      <c r="A20" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="G20" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="H20" t="s">
+        <v>22</v>
+      </c>
+      <c r="I20" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20" s="16">
+        <v>0</v>
+      </c>
+      <c r="L20" s="16">
+        <v>1</v>
+      </c>
+      <c r="M20" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="N20" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="S20" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="T20" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20">
+      <c r="A21" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" t="s">
+        <v>26</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="G21" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="H21" t="s">
+        <v>22</v>
+      </c>
+      <c r="I21" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="K21" s="16">
+        <v>0</v>
+      </c>
+      <c r="L21" s="16">
+        <v>1</v>
+      </c>
+      <c r="M21" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="N21" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="S21" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="T21" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" customFormat="1" spans="1:20">
+      <c r="A22" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F22" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="G22" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="H22" t="s">
+        <v>26</v>
+      </c>
+      <c r="I22" s="11"/>
+      <c r="J22">
+        <v>1</v>
+      </c>
+      <c r="K22" s="16">
+        <v>1</v>
+      </c>
+      <c r="L22" s="16">
+        <v>1</v>
+      </c>
+      <c r="M22" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="N22" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="S22" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="T22" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:T22" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>

--- a/Test upload format/Mudra/IA/2026 - 2027/CP1 26-27.xlsx
+++ b/Test upload format/Mudra/IA/2026 - 2027/CP1 26-27.xlsx
@@ -365,24 +365,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -740,7 +728,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -764,16 +752,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -782,87 +770,87 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -876,26 +864,24 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1327,17 +1313,17 @@
       <c r="H2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="9"/>
+      <c r="I2" s="7"/>
       <c r="J2" s="1">
         <v>1</v>
       </c>
-      <c r="K2" s="9">
+      <c r="K2" s="7">
         <v>0</v>
       </c>
-      <c r="L2" s="9">
-        <v>1</v>
-      </c>
-      <c r="M2" s="10" t="s">
+      <c r="L2" s="7">
+        <v>1</v>
+      </c>
+      <c r="M2" s="9" t="s">
         <v>27</v>
       </c>
       <c r="N2" s="7" t="s">
@@ -1351,45 +1337,45 @@
       </c>
     </row>
     <row r="3" s="2" customFormat="1" spans="1:20">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11" t="s">
+      <c r="E3" s="10"/>
+      <c r="F3" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" s="11"/>
+      <c r="G3" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="10"/>
       <c r="J3" s="2">
         <v>1</v>
       </c>
-      <c r="K3" s="11">
+      <c r="K3" s="10">
         <v>0</v>
       </c>
-      <c r="L3" s="11">
-        <v>1</v>
-      </c>
-      <c r="M3" s="14" t="s">
+      <c r="L3" s="10">
+        <v>1</v>
+      </c>
+      <c r="M3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="N3" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="S3" s="11" t="s">
+      <c r="N3" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="S3" s="10" t="s">
         <v>32</v>
       </c>
       <c r="T3" s="2" t="s">
@@ -1397,45 +1383,45 @@
       </c>
     </row>
     <row r="4" s="2" customFormat="1" spans="1:20">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11" t="s">
+      <c r="E4" s="10"/>
+      <c r="F4" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="10" t="s">
         <v>25</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="I4" s="11"/>
+      <c r="I4" s="10"/>
       <c r="J4" s="2">
         <v>1</v>
       </c>
-      <c r="K4" s="11">
+      <c r="K4" s="10">
         <v>0</v>
       </c>
-      <c r="L4" s="11">
-        <v>1</v>
-      </c>
-      <c r="M4" s="14" t="s">
+      <c r="L4" s="10">
+        <v>1</v>
+      </c>
+      <c r="M4" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="N4" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="S4" s="11" t="s">
+      <c r="N4" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="S4" s="10" t="s">
         <v>34</v>
       </c>
       <c r="T4" s="2" t="s">
@@ -1443,46 +1429,46 @@
       </c>
     </row>
     <row r="5" spans="1:20">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="13" t="s">
         <v>30</v>
       </c>
       <c r="D5" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="13" t="s">
         <v>25</v>
       </c>
       <c r="H5" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="11" t="s">
+      <c r="I5" s="10" t="s">
         <v>23</v>
       </c>
       <c r="J5">
         <v>1</v>
       </c>
-      <c r="K5" s="16">
+      <c r="K5" s="14">
         <v>0</v>
       </c>
-      <c r="L5" s="16">
-        <v>1</v>
-      </c>
-      <c r="M5" s="17" t="s">
+      <c r="L5" s="14">
+        <v>1</v>
+      </c>
+      <c r="M5" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="N5" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="S5" s="15" t="s">
+      <c r="N5" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="S5" s="13" t="s">
         <v>32</v>
       </c>
       <c r="T5" t="s">
@@ -1490,46 +1476,46 @@
       </c>
     </row>
     <row r="6" spans="1:20">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="13" t="s">
         <v>30</v>
       </c>
       <c r="D6" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="15" t="s">
+      <c r="F6" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="15" t="s">
+      <c r="G6" s="13" t="s">
         <v>25</v>
       </c>
       <c r="H6" t="s">
         <v>22</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" s="10" t="s">
         <v>23</v>
       </c>
       <c r="J6">
         <v>1</v>
       </c>
-      <c r="K6" s="16">
+      <c r="K6" s="14">
         <v>0</v>
       </c>
-      <c r="L6" s="16">
-        <v>1</v>
-      </c>
-      <c r="M6" s="17" t="s">
+      <c r="L6" s="14">
+        <v>1</v>
+      </c>
+      <c r="M6" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="N6" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="S6" s="15" t="s">
+      <c r="N6" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="S6" s="13" t="s">
         <v>34</v>
       </c>
       <c r="T6" t="s">
@@ -1537,46 +1523,46 @@
       </c>
     </row>
     <row r="7" spans="1:20">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="13" t="s">
         <v>30</v>
       </c>
       <c r="D7" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="F7" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="G7" s="13" t="s">
         <v>25</v>
       </c>
       <c r="H7" t="s">
         <v>22</v>
       </c>
-      <c r="I7" s="11" t="s">
+      <c r="I7" s="10" t="s">
         <v>23</v>
       </c>
       <c r="J7">
         <v>1</v>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="14">
         <v>0</v>
       </c>
-      <c r="L7" s="16">
-        <v>1</v>
-      </c>
-      <c r="M7" s="17" t="s">
+      <c r="L7" s="14">
+        <v>1</v>
+      </c>
+      <c r="M7" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="N7" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="S7" s="15" t="s">
+      <c r="N7" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="S7" s="13" t="s">
         <v>28</v>
       </c>
       <c r="T7" t="s">
@@ -1584,46 +1570,46 @@
       </c>
     </row>
     <row r="8" spans="1:20">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="13" t="s">
         <v>30</v>
       </c>
       <c r="D8" t="s">
         <v>26</v>
       </c>
-      <c r="F8" s="15" t="s">
+      <c r="F8" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="G8" s="13" t="s">
         <v>25</v>
       </c>
       <c r="H8" t="s">
         <v>22</v>
       </c>
-      <c r="I8" s="11" t="s">
+      <c r="I8" s="10" t="s">
         <v>23</v>
       </c>
       <c r="J8">
         <v>1</v>
       </c>
-      <c r="K8" s="16">
+      <c r="K8" s="14">
         <v>0</v>
       </c>
-      <c r="L8" s="16">
-        <v>1</v>
-      </c>
-      <c r="M8" s="17" t="s">
+      <c r="L8" s="14">
+        <v>1</v>
+      </c>
+      <c r="M8" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="N8" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="S8" s="15" t="s">
+      <c r="N8" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="S8" s="13" t="s">
         <v>32</v>
       </c>
       <c r="T8" t="s">
@@ -1631,46 +1617,46 @@
       </c>
     </row>
     <row r="9" spans="1:20">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="13" t="s">
         <v>30</v>
       </c>
       <c r="D9" t="s">
         <v>26</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="F9" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="G9" s="15" t="s">
+      <c r="G9" s="13" t="s">
         <v>25</v>
       </c>
       <c r="H9" t="s">
         <v>22</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="I9" s="10" t="s">
         <v>23</v>
       </c>
       <c r="J9">
         <v>1</v>
       </c>
-      <c r="K9" s="16">
+      <c r="K9" s="14">
         <v>0</v>
       </c>
-      <c r="L9" s="16">
-        <v>1</v>
-      </c>
-      <c r="M9" s="17" t="s">
+      <c r="L9" s="14">
+        <v>1</v>
+      </c>
+      <c r="M9" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="N9" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="S9" s="15" t="s">
+      <c r="N9" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="S9" s="13" t="s">
         <v>34</v>
       </c>
       <c r="T9" t="s">
@@ -1678,46 +1664,46 @@
       </c>
     </row>
     <row r="10" spans="1:20">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="13" t="s">
         <v>30</v>
       </c>
       <c r="D10" t="s">
         <v>26</v>
       </c>
-      <c r="F10" s="15" t="s">
+      <c r="F10" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="15" t="s">
+      <c r="G10" s="13" t="s">
         <v>25</v>
       </c>
       <c r="H10" t="s">
         <v>22</v>
       </c>
-      <c r="I10" s="11" t="s">
+      <c r="I10" s="10" t="s">
         <v>23</v>
       </c>
       <c r="J10">
         <v>1</v>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="14">
         <v>0</v>
       </c>
-      <c r="L10" s="16">
-        <v>1</v>
-      </c>
-      <c r="M10" s="17" t="s">
+      <c r="L10" s="14">
+        <v>1</v>
+      </c>
+      <c r="M10" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="N10" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="S10" s="15" t="s">
+      <c r="N10" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="S10" s="13" t="s">
         <v>28</v>
       </c>
       <c r="T10" t="s">
@@ -1725,46 +1711,46 @@
       </c>
     </row>
     <row r="11" spans="1:20">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="13" t="s">
         <v>30</v>
       </c>
       <c r="D11" t="s">
         <v>26</v>
       </c>
-      <c r="F11" s="15" t="s">
+      <c r="F11" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="G11" s="15" t="s">
+      <c r="G11" s="13" t="s">
         <v>25</v>
       </c>
       <c r="H11" t="s">
         <v>22</v>
       </c>
-      <c r="I11" s="11" t="s">
+      <c r="I11" s="10" t="s">
         <v>23</v>
       </c>
       <c r="J11">
         <v>1</v>
       </c>
-      <c r="K11" s="16">
+      <c r="K11" s="14">
         <v>0</v>
       </c>
-      <c r="L11" s="16">
-        <v>1</v>
-      </c>
-      <c r="M11" s="17" t="s">
+      <c r="L11" s="14">
+        <v>1</v>
+      </c>
+      <c r="M11" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="N11" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="S11" s="15" t="s">
+      <c r="N11" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="S11" s="13" t="s">
         <v>32</v>
       </c>
       <c r="T11" t="s">
@@ -1772,46 +1758,46 @@
       </c>
     </row>
     <row r="12" spans="1:20">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="13" t="s">
         <v>30</v>
       </c>
       <c r="D12" t="s">
         <v>26</v>
       </c>
-      <c r="F12" s="15" t="s">
+      <c r="F12" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="G12" s="15" t="s">
+      <c r="G12" s="13" t="s">
         <v>25</v>
       </c>
       <c r="H12" t="s">
         <v>22</v>
       </c>
-      <c r="I12" s="11" t="s">
+      <c r="I12" s="10" t="s">
         <v>23</v>
       </c>
       <c r="J12">
         <v>1</v>
       </c>
-      <c r="K12" s="16">
+      <c r="K12" s="14">
         <v>0</v>
       </c>
-      <c r="L12" s="16">
-        <v>1</v>
-      </c>
-      <c r="M12" s="17" t="s">
+      <c r="L12" s="14">
+        <v>1</v>
+      </c>
+      <c r="M12" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="N12" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="S12" s="15" t="s">
+      <c r="N12" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="S12" s="13" t="s">
         <v>34</v>
       </c>
       <c r="T12" t="s">
@@ -1819,46 +1805,46 @@
       </c>
     </row>
     <row r="13" spans="1:20">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="13" t="s">
         <v>30</v>
       </c>
       <c r="D13" t="s">
         <v>26</v>
       </c>
-      <c r="F13" s="15" t="s">
+      <c r="F13" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="G13" s="15" t="s">
+      <c r="G13" s="13" t="s">
         <v>25</v>
       </c>
       <c r="H13" t="s">
         <v>22</v>
       </c>
-      <c r="I13" s="11" t="s">
+      <c r="I13" s="10" t="s">
         <v>23</v>
       </c>
       <c r="J13">
         <v>1</v>
       </c>
-      <c r="K13" s="16">
+      <c r="K13" s="14">
         <v>0</v>
       </c>
-      <c r="L13" s="16">
-        <v>1</v>
-      </c>
-      <c r="M13" s="17" t="s">
+      <c r="L13" s="14">
+        <v>1</v>
+      </c>
+      <c r="M13" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="N13" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="S13" s="15" t="s">
+      <c r="N13" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="S13" s="13" t="s">
         <v>28</v>
       </c>
       <c r="T13" t="s">
@@ -1866,46 +1852,46 @@
       </c>
     </row>
     <row r="14" spans="1:20">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="13" t="s">
         <v>30</v>
       </c>
       <c r="D14" t="s">
         <v>26</v>
       </c>
-      <c r="F14" s="15" t="s">
+      <c r="F14" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="G14" s="15" t="s">
+      <c r="G14" s="13" t="s">
         <v>25</v>
       </c>
       <c r="H14" t="s">
         <v>22</v>
       </c>
-      <c r="I14" s="11" t="s">
+      <c r="I14" s="10" t="s">
         <v>23</v>
       </c>
       <c r="J14">
         <v>1</v>
       </c>
-      <c r="K14" s="16">
+      <c r="K14" s="14">
         <v>0</v>
       </c>
-      <c r="L14" s="16">
-        <v>1</v>
-      </c>
-      <c r="M14" s="17" t="s">
+      <c r="L14" s="14">
+        <v>1</v>
+      </c>
+      <c r="M14" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="N14" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="S14" s="15" t="s">
+      <c r="N14" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="S14" s="13" t="s">
         <v>32</v>
       </c>
       <c r="T14" t="s">
@@ -1913,46 +1899,46 @@
       </c>
     </row>
     <row r="15" spans="1:20">
-      <c r="A15" s="15" t="s">
+      <c r="A15" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="13" t="s">
         <v>30</v>
       </c>
       <c r="D15" t="s">
         <v>26</v>
       </c>
-      <c r="F15" s="15" t="s">
+      <c r="F15" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="G15" s="15" t="s">
+      <c r="G15" s="13" t="s">
         <v>25</v>
       </c>
       <c r="H15" t="s">
         <v>22</v>
       </c>
-      <c r="I15" s="11" t="s">
+      <c r="I15" s="10" t="s">
         <v>23</v>
       </c>
       <c r="J15">
         <v>1</v>
       </c>
-      <c r="K15" s="16">
+      <c r="K15" s="14">
         <v>0</v>
       </c>
-      <c r="L15" s="16">
-        <v>1</v>
-      </c>
-      <c r="M15" s="17" t="s">
+      <c r="L15" s="14">
+        <v>1</v>
+      </c>
+      <c r="M15" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="N15" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="S15" s="15" t="s">
+      <c r="N15" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="S15" s="13" t="s">
         <v>34</v>
       </c>
       <c r="T15" t="s">
@@ -1960,46 +1946,46 @@
       </c>
     </row>
     <row r="16" spans="1:20">
-      <c r="A16" s="15" t="s">
+      <c r="A16" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="13" t="s">
         <v>30</v>
       </c>
       <c r="D16" t="s">
         <v>26</v>
       </c>
-      <c r="F16" s="15" t="s">
+      <c r="F16" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="G16" s="15" t="s">
+      <c r="G16" s="13" t="s">
         <v>25</v>
       </c>
       <c r="H16" t="s">
         <v>22</v>
       </c>
-      <c r="I16" s="11" t="s">
+      <c r="I16" s="10" t="s">
         <v>23</v>
       </c>
       <c r="J16">
         <v>1</v>
       </c>
-      <c r="K16" s="16">
+      <c r="K16" s="14">
         <v>0</v>
       </c>
-      <c r="L16" s="16">
-        <v>1</v>
-      </c>
-      <c r="M16" s="17" t="s">
+      <c r="L16" s="14">
+        <v>1</v>
+      </c>
+      <c r="M16" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="N16" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="S16" s="15" t="s">
+      <c r="N16" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="S16" s="13" t="s">
         <v>28</v>
       </c>
       <c r="T16" t="s">
@@ -2007,46 +1993,46 @@
       </c>
     </row>
     <row r="17" spans="1:20">
-      <c r="A17" s="15" t="s">
+      <c r="A17" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C17" s="13" t="s">
         <v>30</v>
       </c>
       <c r="D17" t="s">
         <v>26</v>
       </c>
-      <c r="F17" s="15" t="s">
+      <c r="F17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="G17" s="15" t="s">
+      <c r="G17" s="13" t="s">
         <v>25</v>
       </c>
       <c r="H17" t="s">
         <v>22</v>
       </c>
-      <c r="I17" s="11" t="s">
+      <c r="I17" s="10" t="s">
         <v>23</v>
       </c>
       <c r="J17">
         <v>1</v>
       </c>
-      <c r="K17" s="16">
+      <c r="K17" s="14">
         <v>0</v>
       </c>
-      <c r="L17" s="16">
-        <v>1</v>
-      </c>
-      <c r="M17" s="17" t="s">
+      <c r="L17" s="14">
+        <v>1</v>
+      </c>
+      <c r="M17" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="N17" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="S17" s="15" t="s">
+      <c r="N17" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="S17" s="13" t="s">
         <v>32</v>
       </c>
       <c r="T17" t="s">
@@ -2054,46 +2040,46 @@
       </c>
     </row>
     <row r="18" spans="1:20">
-      <c r="A18" s="15" t="s">
+      <c r="A18" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="13" t="s">
         <v>30</v>
       </c>
       <c r="D18" t="s">
         <v>26</v>
       </c>
-      <c r="F18" s="15" t="s">
+      <c r="F18" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="G18" s="15" t="s">
+      <c r="G18" s="13" t="s">
         <v>25</v>
       </c>
       <c r="H18" t="s">
         <v>22</v>
       </c>
-      <c r="I18" s="11" t="s">
+      <c r="I18" s="10" t="s">
         <v>23</v>
       </c>
       <c r="J18">
         <v>1</v>
       </c>
-      <c r="K18" s="16">
+      <c r="K18" s="14">
         <v>0</v>
       </c>
-      <c r="L18" s="16">
-        <v>1</v>
-      </c>
-      <c r="M18" s="17" t="s">
+      <c r="L18" s="14">
+        <v>1</v>
+      </c>
+      <c r="M18" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="N18" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="S18" s="15" t="s">
+      <c r="N18" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="S18" s="13" t="s">
         <v>34</v>
       </c>
       <c r="T18" t="s">
@@ -2101,46 +2087,46 @@
       </c>
     </row>
     <row r="19" spans="1:20">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="13" t="s">
         <v>30</v>
       </c>
       <c r="D19" t="s">
         <v>26</v>
       </c>
-      <c r="F19" s="15" t="s">
+      <c r="F19" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="G19" s="15" t="s">
+      <c r="G19" s="13" t="s">
         <v>25</v>
       </c>
       <c r="H19" t="s">
         <v>22</v>
       </c>
-      <c r="I19" s="11" t="s">
+      <c r="I19" s="10" t="s">
         <v>23</v>
       </c>
       <c r="J19">
         <v>1</v>
       </c>
-      <c r="K19" s="16">
+      <c r="K19" s="14">
         <v>0</v>
       </c>
-      <c r="L19" s="16">
-        <v>1</v>
-      </c>
-      <c r="M19" s="17" t="s">
+      <c r="L19" s="14">
+        <v>1</v>
+      </c>
+      <c r="M19" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="N19" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="S19" s="15" t="s">
+      <c r="N19" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="S19" s="13" t="s">
         <v>28</v>
       </c>
       <c r="T19" t="s">
@@ -2148,46 +2134,46 @@
       </c>
     </row>
     <row r="20" spans="1:20">
-      <c r="A20" s="15" t="s">
+      <c r="A20" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="13" t="s">
         <v>30</v>
       </c>
       <c r="D20" t="s">
         <v>26</v>
       </c>
-      <c r="F20" s="15" t="s">
+      <c r="F20" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="G20" s="15" t="s">
+      <c r="G20" s="13" t="s">
         <v>25</v>
       </c>
       <c r="H20" t="s">
         <v>22</v>
       </c>
-      <c r="I20" s="11" t="s">
+      <c r="I20" s="10" t="s">
         <v>23</v>
       </c>
       <c r="J20">
         <v>1</v>
       </c>
-      <c r="K20" s="16">
+      <c r="K20" s="14">
         <v>0</v>
       </c>
-      <c r="L20" s="16">
-        <v>1</v>
-      </c>
-      <c r="M20" s="17" t="s">
+      <c r="L20" s="14">
+        <v>1</v>
+      </c>
+      <c r="M20" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="N20" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="S20" s="15" t="s">
+      <c r="N20" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="S20" s="13" t="s">
         <v>32</v>
       </c>
       <c r="T20" t="s">
@@ -2195,46 +2181,46 @@
       </c>
     </row>
     <row r="21" spans="1:20">
-      <c r="A21" s="15" t="s">
+      <c r="A21" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C21" s="13" t="s">
         <v>30</v>
       </c>
       <c r="D21" t="s">
         <v>26</v>
       </c>
-      <c r="F21" s="15" t="s">
+      <c r="F21" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="G21" s="15" t="s">
+      <c r="G21" s="13" t="s">
         <v>25</v>
       </c>
       <c r="H21" t="s">
         <v>22</v>
       </c>
-      <c r="I21" s="11" t="s">
+      <c r="I21" s="10" t="s">
         <v>23</v>
       </c>
       <c r="J21">
         <v>1</v>
       </c>
-      <c r="K21" s="16">
+      <c r="K21" s="14">
         <v>0</v>
       </c>
-      <c r="L21" s="16">
-        <v>1</v>
-      </c>
-      <c r="M21" s="17" t="s">
+      <c r="L21" s="14">
+        <v>1</v>
+      </c>
+      <c r="M21" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="N21" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="S21" s="15" t="s">
+      <c r="N21" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="S21" s="13" t="s">
         <v>34</v>
       </c>
       <c r="T21" t="s">
@@ -2242,47 +2228,47 @@
       </c>
     </row>
     <row r="22" customFormat="1" spans="1:20">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="B22" s="18" t="s">
+      <c r="B22" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="C22" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="19" t="s">
+      <c r="D22" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="E22" s="11" t="s">
+      <c r="E22" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F22" s="18" t="s">
+      <c r="F22" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="G22" s="18" t="s">
+      <c r="G22" s="16" t="s">
         <v>25</v>
       </c>
       <c r="H22" t="s">
         <v>26</v>
       </c>
-      <c r="I22" s="11"/>
+      <c r="I22" s="10"/>
       <c r="J22">
         <v>1</v>
       </c>
-      <c r="K22" s="16">
-        <v>1</v>
-      </c>
-      <c r="L22" s="16">
-        <v>1</v>
-      </c>
-      <c r="M22" s="20" t="s">
+      <c r="K22" s="14">
+        <v>1</v>
+      </c>
+      <c r="L22" s="14">
+        <v>1</v>
+      </c>
+      <c r="M22" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="N22" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="S22" s="18" t="s">
+      <c r="N22" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="S22" s="16" t="s">
         <v>32</v>
       </c>
       <c r="T22" t="s">
